--- a/JsonConverter/ExcelFiles/Object.xlsx
+++ b/JsonConverter/ExcelFiles/Object.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17235" windowHeight="13785"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23175" windowHeight="13785"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Table_Active" sheetId="1" r:id="rId4"/>
@@ -14,12 +14,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+  <x:si>
+    <x:t>ex_fixer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>누군가의 연구 기록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NotePopupUI</x:t>
+  </x:si>
   <x:si>
     <x:t>PopupType</x:t>
   </x:si>
   <x:si>
-    <x:t>NotePopupUI</x:t>
+    <x:t>red_fixer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>origin_fixer_01</x:t>
   </x:si>
   <x:si>
     <x:t>generator_01</x:t>
@@ -28,64 +40,73 @@
     <x:t>note_someone_01</x:t>
   </x:si>
   <x:si>
+    <x:t>FixerPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>볼트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>픽스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>ControlRepairPopupUI</x:t>
   </x:si>
   <x:si>
     <x:t>ElectricRepairPopupUI</x:t>
   </x:si>
   <x:si>
+    <x:t>temp_controller_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AirRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>research_someone_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HiddenNotePopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>censer_controler_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
     <x:t>oxygen_supplier_01</x:t>
   </x:si>
   <x:si>
-    <x:t>research_someone_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>temp_controller_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>censer_controler_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AirRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>누군가의 연구 기록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HiddenNotePopupUI</x:t>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산소 공급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>누군가의 쪽지</x:t>
   </x:si>
   <x:si>
     <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
     <x:t>향로 제어</x:t>
   </x:si>
   <x:si>
+    <x:t>암스트숏</x:t>
+  </x:si>
+  <x:si>
     <x:t>전력 공급</x:t>
   </x:si>
   <x:si>
-    <x:t>산소 공급</x:t>
-  </x:si>
-  <x:si>
     <x:t>온도 제어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>누군가의 쪽지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -961,7 +982,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -972,13 +993,13 @@
     </x:row>
     <x:row r="2" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="1"/>
@@ -987,13 +1008,13 @@
     </x:row>
     <x:row r="3" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1002,13 +1023,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1017,13 +1038,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1032,13 +1053,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1047,13 +1068,13 @@
     </x:row>
     <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
@@ -1062,13 +1083,13 @@
     </x:row>
     <x:row r="8" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="6"/>
@@ -1077,13 +1098,13 @@
     </x:row>
     <x:row r="9" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="5"/>
       <x:c r="E9" s="5"/>
@@ -1091,27 +1112,45 @@
       <x:c r="G9" s="5"/>
     </x:row>
     <x:row r="10" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A10" s="3"/>
-      <x:c r="B10" s="3"/>
-      <x:c r="C10" s="3"/>
+      <x:c r="A10" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="D10" s="3"/>
       <x:c r="E10" s="3"/>
       <x:c r="F10" s="3"/>
       <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A11" s="3"/>
-      <x:c r="B11" s="6"/>
-      <x:c r="C11" s="6"/>
+      <x:c r="A11" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="D11" s="6"/>
       <x:c r="E11" s="6"/>
       <x:c r="F11" s="6"/>
       <x:c r="G11" s="6"/>
     </x:row>
     <x:row r="12" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A12" s="3"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
+      <x:c r="A12" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>

--- a/JsonConverter/ExcelFiles/Object.xlsx
+++ b/JsonConverter/ExcelFiles/Object.xlsx
@@ -14,7 +14,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+  <x:si>
+    <x:t>TempRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>temp_controller_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>research_someone_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>oxygen_supplier_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HiddenNotePopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>censer_controler_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AirRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>note_someone_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>red_fixer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>origin_fixer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>generator_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FixerPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectricRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ControlRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>볼트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>픽스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침대</x:t>
+  </x:si>
   <x:si>
     <x:t>ex_fixer_01</x:t>
   </x:si>
@@ -28,85 +82,37 @@
     <x:t>PopupType</x:t>
   </x:si>
   <x:si>
-    <x:t>red_fixer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>origin_fixer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>generator_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>note_someone_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FixerPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>볼트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>픽스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ControlRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ElectricRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>temp_controller_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AirRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>research_someone_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HiddenNotePopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>censer_controler_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>oxygen_supplier_01</x:t>
+    <x:t>암스트숏</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산소 공급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>온도 제어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>향로 제어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전력 공급</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>산소 공급</x:t>
-  </x:si>
-  <x:si>
     <x:t>누군가의 쪽지</x:t>
   </x:si>
   <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>향로 제어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>암스트숏</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전력 공급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>온도 제어</x:t>
+    <x:t>bad_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -982,7 +988,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -993,13 +999,13 @@
     </x:row>
     <x:row r="2" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="1"/>
@@ -1008,13 +1014,13 @@
     </x:row>
     <x:row r="3" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1023,13 +1029,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1038,13 +1044,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1053,13 +1059,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1068,13 +1074,13 @@
     </x:row>
     <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
@@ -1086,10 +1092,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="6"/>
@@ -1098,13 +1104,13 @@
     </x:row>
     <x:row r="9" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D9" s="5"/>
       <x:c r="E9" s="5"/>
@@ -1113,13 +1119,13 @@
     </x:row>
     <x:row r="10" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A10" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
       <x:c r="E10" s="3"/>
@@ -1128,13 +1134,13 @@
     </x:row>
     <x:row r="11" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A11" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="6"/>
       <x:c r="E11" s="6"/>
@@ -1143,13 +1149,13 @@
     </x:row>
     <x:row r="12" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A12" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
@@ -1157,8 +1163,12 @@
       <x:c r="G12" s="6"/>
     </x:row>
     <x:row r="13" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A13" s="7"/>
-      <x:c r="B13" s="7"/>
+      <x:c r="A13" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C13" s="7"/>
       <x:c r="D13" s="7"/>
       <x:c r="E13" s="7"/>

--- a/JsonConverter/ExcelFiles/Object.xlsx
+++ b/JsonConverter/ExcelFiles/Object.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23175" windowHeight="13785"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28920" windowHeight="13785"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Table_Active" sheetId="1" r:id="rId4"/>
@@ -14,105 +14,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+  <x:si>
+    <x:t>문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DoorPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectricRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ControlRepairPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>볼트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>픽스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Door_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>temp_controller_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>censer_controler_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>research_someone_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>oxygen_supplier_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HiddenNotePopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AirRepairPopupUI</x:t>
+  </x:si>
   <x:si>
     <x:t>TempRepairPopupUI</x:t>
   </x:si>
   <x:si>
-    <x:t>temp_controller_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>research_someone_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>oxygen_supplier_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HiddenNotePopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>censer_controler_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AirRepairPopupUI</x:t>
+    <x:t>ex_fixer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PopupType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NotePopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>누군가의 연구 기록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>red_fixer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>generator_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FixerPopupUI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>origin_fixer_01</x:t>
   </x:si>
   <x:si>
     <x:t>note_someone_01</x:t>
   </x:si>
   <x:si>
-    <x:t>red_fixer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>origin_fixer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>generator_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FixerPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ElectricRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ControlRepairPopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>볼트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>픽스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ex_fixer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>누군가의 연구 기록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NotePopupUI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PopupType</x:t>
+    <x:t>향로 제어</x:t>
   </x:si>
   <x:si>
     <x:t>암스트숏</x:t>
   </x:si>
   <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
     <x:t>산소 공급</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bad_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>온도 제어</x:t>
+  </x:si>
+  <x:si>
     <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>온도 제어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>향로 제어</x:t>
-  </x:si>
-  <x:si>
     <x:t>전력 공급</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>누군가의 쪽지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bad_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -988,7 +997,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -999,7 +1008,7 @@
     </x:row>
     <x:row r="2" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>29</x:v>
@@ -1014,13 +1023,13 @@
     </x:row>
     <x:row r="3" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1029,13 +1038,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1044,13 +1053,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1059,13 +1068,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1074,13 +1083,13 @@
     </x:row>
     <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
@@ -1089,13 +1098,13 @@
     </x:row>
     <x:row r="8" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="6"/>
@@ -1104,13 +1113,13 @@
     </x:row>
     <x:row r="9" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="5"/>
       <x:c r="E9" s="5"/>
@@ -1119,13 +1128,13 @@
     </x:row>
     <x:row r="10" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A10" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
       <x:c r="E10" s="3"/>
@@ -1134,13 +1143,13 @@
     </x:row>
     <x:row r="11" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A11" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="6"/>
       <x:c r="E11" s="6"/>
@@ -1149,13 +1158,13 @@
     </x:row>
     <x:row r="12" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A12" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
@@ -1164,10 +1173,10 @@
     </x:row>
     <x:row r="13" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A13" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="7"/>
       <x:c r="D13" s="7"/>
@@ -1176,9 +1185,15 @@
       <x:c r="G13" s="7"/>
     </x:row>
     <x:row r="14" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A14" s="7"/>
-      <x:c r="B14" s="7"/>
-      <x:c r="C14" s="7"/>
+      <x:c r="A14" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="D14" s="7"/>
       <x:c r="E14" s="7"/>
       <x:c r="F14" s="7"/>

--- a/JsonConverter/ExcelFiles/Object.xlsx
+++ b/JsonConverter/ExcelFiles/Object.xlsx
@@ -1,130 +1,140 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30317"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Com\Desktop\개발\포크\SunnyHoGaming\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85867b8a770c3dbd/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74A7183A-D732-4886-BD1C-0B9EF0AC8B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23175" windowHeight="13785"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Active" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+  <si>
+    <t>고유 ID</t>
+  </si>
+  <si>
+    <t>(name)</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>PopupType</t>
+  </si>
+  <si>
+    <t>oxygen_supplier_01</t>
+  </si>
+  <si>
+    <t>산소 공급</t>
+  </si>
+  <si>
+    <t>AirRepairPopupUI</t>
+  </si>
+  <si>
+    <t>generator_01</t>
+  </si>
+  <si>
+    <t>전력 공급</t>
+  </si>
+  <si>
+    <t>ElectricRepairPopupUI</t>
+  </si>
+  <si>
+    <t>temp_controller_01</t>
+  </si>
+  <si>
+    <t>온도 제어</t>
+  </si>
   <si>
     <t>TempRepairPopupUI</t>
   </si>
   <si>
-    <t>temp_controller_01</t>
+    <t>censer_controler_01</t>
+  </si>
+  <si>
+    <t>향로 제어</t>
+  </si>
+  <si>
+    <t>ControlRepairPopupUI</t>
+  </si>
+  <si>
+    <t>note_someone_01</t>
+  </si>
+  <si>
+    <t>누군가의 쪽지</t>
+  </si>
+  <si>
+    <t>NotePopupUI</t>
   </si>
   <si>
     <t>research_someone_01</t>
   </si>
   <si>
-    <t>oxygen_supplier_01</t>
+    <t>누군가의 연구 기록</t>
   </si>
   <si>
     <t>HiddenNotePopupUI</t>
   </si>
   <si>
-    <t>censer_controler_01</t>
-  </si>
-  <si>
-    <t>AirRepairPopupUI</t>
-  </si>
-  <si>
-    <t>note_someone_01</t>
+    <t>origin_fixer_01</t>
+  </si>
+  <si>
+    <t>픽스</t>
+  </si>
+  <si>
+    <t>FixerPopupUI</t>
+  </si>
+  <si>
+    <t>ex_fixer_01</t>
+  </si>
+  <si>
+    <t>암스트숏</t>
   </si>
   <si>
     <t>red_fixer_01</t>
   </si>
   <si>
-    <t>origin_fixer_01</t>
-  </si>
-  <si>
-    <t>generator_01</t>
-  </si>
-  <si>
-    <t>FixerPopupUI</t>
-  </si>
-  <si>
-    <t>ElectricRepairPopupUI</t>
-  </si>
-  <si>
-    <t>ControlRepairPopupUI</t>
-  </si>
-  <si>
     <t>볼트</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>픽스</t>
+    <t>bad_01</t>
   </si>
   <si>
     <t>침대</t>
-  </si>
-  <si>
-    <t>ex_fixer_01</t>
-  </si>
-  <si>
-    <t>누군가의 연구 기록</t>
-  </si>
-  <si>
-    <t>NotePopupUI</t>
-  </si>
-  <si>
-    <t>PopupType</t>
-  </si>
-  <si>
-    <t>암스트숏</t>
-  </si>
-  <si>
-    <t>산소 공급</t>
-  </si>
-  <si>
-    <t>고유 ID</t>
-  </si>
-  <si>
-    <t>온도 제어</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>향로 제어</t>
-  </si>
-  <si>
-    <t>전력 공급</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(name)</t>
-  </si>
-  <si>
-    <t>누군가의 쪽지</t>
-  </si>
-  <si>
-    <t>bad_01</t>
-  </si>
-  <si>
-    <t>관제 시스템</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RepairDisplayUI</t>
   </si>
   <si>
     <r>
@@ -150,12 +160,31 @@
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>관제 시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepairDisplayUI</t>
+  </si>
+  <si>
+    <t>Door_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>문</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoorPopupUI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -193,6 +222,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="7">
@@ -261,7 +297,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -286,6 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -500,7 +537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G997"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
@@ -515,7 +552,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -526,13 +563,13 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -541,13 +578,13 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -556,13 +593,13 @@
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -571,13 +608,13 @@
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -586,13 +623,13 @@
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -601,13 +638,13 @@
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -616,10 +653,10 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>20</v>
@@ -631,13 +668,13 @@
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -646,13 +683,13 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -661,13 +698,13 @@
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -676,13 +713,13 @@
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -691,10 +728,10 @@
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -704,13 +741,13 @@
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -718,9 +755,15 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>38</v>
+      </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
